--- a/bases de datos planes y programas/planes_orientación.xlsx
+++ b/bases de datos planes y programas/planes_orientación.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet name="Planes Curriculares" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Planes Curriculares'!$A$1:$G$76</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -469,12 +471,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="52" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="64" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -3699,6 +3701,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G76"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>